--- a/data/trans_dic/P25C$otrosprofesionales_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P25C$otrosprofesionales_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, al menos, acupuntura u homeparía</t>
+          <t>Población cuyo método para dejar de fumar fue, al menos, acupuntura u homeparía (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,0; 2,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 2,14</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,19</t>
+          <t>0,0; 5,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,11</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 6,01</t>
+          <t>0,22; 7,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,3</t>
+          <t>0,3; 3,11</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,54</t>
+          <t>0,32; 3,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,34</t>
+          <t>0,92; 5,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,25</t>
+          <t>0,92; 3,37</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,07</t>
+          <t>0,1; 1,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,21</t>
+          <t>0,93; 3,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,4</t>
+          <t>0,4; 1,41</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, al menos, acupuntura u homeparía</t>
+          <t>Población cuyo método para dejar de fumar fue, al menos, acupuntura u homeparía (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2941</t>
+          <t>0; 3020</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1122</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2871</t>
+          <t>0; 3506</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3987</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3497</t>
+          <t>0; 4262</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4621</t>
+          <t>0; 4551</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4403</t>
+          <t>0; 3692</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>166; 4499</t>
+          <t>164; 5399</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>706; 7146</t>
+          <t>659; 6733</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>623; 6894</t>
+          <t>623; 6815</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1219; 6949</t>
+          <t>1193; 7462</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2837; 10553</t>
+          <t>2982; 10930</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>832; 9049</t>
+          <t>834; 9150</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3141; 10839</t>
+          <t>3137; 11316</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4438; 16629</t>
+          <t>4726; 16793</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C$otrosprofesionales_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P25C$otrosprofesionales_2023-Habitat-trans_dic.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 2,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,14</t>
+          <t>0,0; 2,38</t>
         </is>
       </c>
     </row>
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,11</t>
+          <t>0,0; 5,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 1,73</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 7,21</t>
+          <t>0,8; 7,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,11</t>
+          <t>0,29; 2,84</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,5</t>
+          <t>0,45; 4,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,74</t>
+          <t>0,91; 5,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,37</t>
+          <t>1,08; 3,66</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,08</t>
+          <t>0,3; 1,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,35</t>
+          <t>1,07; 3,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,41</t>
+          <t>0,72; 1,9</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>691</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>691</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3020</t>
+          <t>0; 2886</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3506</t>
+          <t>0; 4186</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1257</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4262</t>
+          <t>0; 4640</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4551</t>
+          <t>0; 4515</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>971</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2159</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2496</t>
+          <t>3130</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3692</t>
+          <t>0; 4735</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>164; 5399</t>
+          <t>670; 5967</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>659; 6733</t>
+          <t>731; 7036</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3261</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>3677</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5841</t>
+          <t>6938</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>623; 6815</t>
+          <t>899; 8803</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1193; 7462</t>
+          <t>1268; 7310</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2982; 10930</t>
+          <t>3689; 12498</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>12016</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>834; 9150</t>
+          <t>2000; 10157</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3137; 11316</t>
+          <t>3902; 12254</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4726; 16793</t>
+          <t>7383; 19530</t>
         </is>
       </c>
     </row>
